--- a/data/processed/harmonization/Carbon__Particulate_organic_matter_carbon/10.15485_1994876/10.15485_1994876_soil_Carbon__Particulate_organic_matter_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Particulate_organic_matter_carbon/10.15485_1994876/10.15485_1994876_soil_Carbon__Particulate_organic_matter_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:18</t>
+          <t>ER-MCB1:30:18</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:44</t>
+          <t>ER-MCB1:30:44</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:60</t>
+          <t>ER-MCB1:30:60</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:31</t>
+          <t>ER-MCB2:30:31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:36</t>
+          <t>ER-MCB2:30:36</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:43</t>
+          <t>ER-MCB2:30:43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:20</t>
+          <t>ER-MCB3:30:20</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:21</t>
+          <t>ER-MCB3:30:21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:25</t>
+          <t>ER-MCB3:30:25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:28</t>
+          <t>ER-MCB1:70:28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:49</t>
+          <t>ER-MCB1:70:49</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:65</t>
+          <t>ER-MCB1:70:65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:46</t>
+          <t>ER-MCB2:70:46</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:50</t>
+          <t>ER-MCB2:70:50</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:52</t>
+          <t>ER-MCB2:70:52</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:17</t>
+          <t>ER-MCB3:70:17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:27</t>
+          <t>ER-MCB3:70:27</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:55</t>
+          <t>ER-MCB3:70:55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
